--- a/data/MEL_Indicator_Reference.xlsx
+++ b/data/MEL_Indicator_Reference.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MEL_Indicators" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species_by_Sector" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure_by_Sector" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3182,6 +3183,312 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Aquaculture Type</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Farm Structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Longline (surface)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Longline (subsurface)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Raft / floating</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Off-bottom (monoline / pegs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Bottom culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Land-based tank or pond</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>IMTA infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Seaweed</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Floating cage / tray</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Bouchot / pole culture</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Intertidal rack-and-bag</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Trestle / trays (intertidal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>On-bottom cages</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Suspended lantern net</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Suspended longline (mussel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Pearl net / spat collector</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Floating bag (oyster)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Off-bottom suspended oyster (BC-style)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Intertidal net-over-substrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Raft / hanging rope</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Bottom culture (clam seeded substrate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Mollusk</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Reef / on-bottom structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Not gear-specific</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/data/MEL_Indicator_Reference.xlsx
+++ b/data/MEL_Indicator_Reference.xlsx
@@ -10,9 +10,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MEL_Indicators" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species_by_Sector" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Structure_by_Sector" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monitoring_Approaches" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Monitoring_Approaches'!$A$1:$F$57</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +56,14 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -81,8 +90,58 @@
         <fgColor rgb="00FBF1E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E5F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF3F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBF2E3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3ECF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDECEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF6F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF1F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -104,11 +163,25 @@
         <color rgb="00D7DEE0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -132,6 +205,63 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3489,7 +3619,1582 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:F57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Category_Order</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Sub_Method</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>AG_Tags</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>AK_Keywords</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Temperature / salinity</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry;In-situ sensors</t>
+        </is>
+      </c>
+      <c r="E2" s="13" t="inlineStr">
+        <is>
+          <t>temperature;salinity</t>
+        </is>
+      </c>
+      <c r="F2" s="13" t="inlineStr">
+        <is>
+          <t>In-situ probe/sonde or CTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>Dissolved oxygen</t>
+        </is>
+      </c>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry;In-situ sensors</t>
+        </is>
+      </c>
+      <c r="E3" s="13" t="inlineStr">
+        <is>
+          <t>dissolved oxygen;winkler</t>
+        </is>
+      </c>
+      <c r="F3" s="13" t="inlineStr">
+        <is>
+          <t>Probe or Winkler titration</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>In-situ probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Water clarity / turbidity (Secchi)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>secchi;turbidity;transparency;clarity</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Dissolved nutrients (N &amp; P)</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>nitrate;nitrite;ammonium;phosphate;silicate;dissolved inorganic</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Autoanalyser / colourimetric</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Total nitrogen / total phosphorus</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>total nitrogen;total phosphorus;persulfate</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Chlorophyll-a (water)</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>chlorophyll-a;gf/f;fluorometer</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Filtered &amp; extracted</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Suspended solids (TSS / SPM)</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>suspended solids;suspended particulate;gravimetric</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Dissolved / total organic carbon</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>organic carbon;doc;toc</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>BOD / COD</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>bod;chemical oxygen demand</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Carbonate system (pH / OA)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Carbonate chemistry;Water chemistry</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>carbonate;pco2;dic;dissolved inorganic carbon;alkalinity;acidification;co2sys</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>pCO2, DIC, total alkalinity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Faecal coliforms / E. coli</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>faecal;coliform;e. coli;most-probable-number</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>Shellfish-water microbial</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Water chemistry</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>Continuous moored sensors</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>In-situ sensors;Water chemistry</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>sensor string;moored;log;autonomous;continuous</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Autonomous logging buoy/string</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Seabed / sediment</t>
+        </is>
+      </c>
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>Grain size / particle size</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>Sediment sampling</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>grain size;particle size;grab;core</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Seabed / sediment</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Sediment chemistry (OC / TN / redox / AVS)</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="inlineStr">
+        <is>
+          <t>Sediment sampling</t>
+        </is>
+      </c>
+      <c r="E16" s="15" t="inlineStr">
+        <is>
+          <t>organic carbon;redox;sulphide;acid-volatile;total nitrogen;organic matter</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Seabed / sediment</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
+          <t>Benthic infauna community</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <t>Benthic infauna sampling;Sediment sampling</t>
+        </is>
+      </c>
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>infauna;van veen;sieve;ambi;iti;macrobenthos;macrofauna</t>
+        </is>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Grab + sieve + ID; AMBI/ITI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Seabed / sediment</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>Sediment / benthic flux incubation</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>Benthic flux incubation;Sediment sampling</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>flux;incubat;core;denitrif;dnra;15n;benthic chamber</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>O2/N/P flux, denitrification</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Seabed / sediment</t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>Biodeposition traps</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t>Sediment sampling</t>
+        </is>
+      </c>
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>biodeposit;trap</t>
+        </is>
+      </c>
+      <c r="F19" s="15" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Seabed / sediment</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
+        <is>
+          <t>Sediment-profile imaging (SPI)</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="inlineStr">
+        <is>
+          <t>Sediment sampling</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr">
+        <is>
+          <t>sediment-profile;spi;profile imaging</t>
+        </is>
+      </c>
+      <c r="F20" s="15" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Seabed / sediment</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>MOM-B condition survey</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Sediment sampling</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>mom-b;redox;sensory;condition class</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Seabed / sediment</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Bed stability / erosion</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>Sediment sampling;Hydrodynamic measurement</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>erosion;shear stress;erodibility;bed-level</t>
+        </is>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Critical shear stress / erosion chamber</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Visual census / belt transects</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>Visual survey;Diver/video sampling</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="inlineStr">
+        <is>
+          <t>visual census;belt transect;diver;snorkel;fish count</t>
+        </is>
+      </c>
+      <c r="F23" s="17" t="inlineStr">
+        <is>
+          <t>Diver / snorkel fish counts</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Baited remote underwater video (BRUV)</t>
+        </is>
+      </c>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>BRUVs / video;Diver/video sampling;Visual survey</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="inlineStr">
+        <is>
+          <t>bruv;baited;maxn</t>
+        </is>
+      </c>
+      <c r="F24" s="17" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Time-lapse / GoPro cameras</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>BRUVs / video;Visual survey</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>time-lapse;gopro;camera</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>Towed video / ROV</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>BRUVs / video</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>towed video;rov</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>Epibiota on lines / structures</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>epibiot;epibiont;fouling;quadrat;cover;scrape</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>Quadrat scrape, cover, biomass</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>Epifauna on crop / rope</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>epifauna;kelp;rope;holdfast;strip</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>Strip, sieve, ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Settlement plates / artificial substrata</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Visual survey;eDNA</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>settlement plate;artificial substrat</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>Invertebrate collectors / fauna traps</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>collector;fauna trap;sponge;untwisted-rope</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>Nets &amp; baited traps</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>gill net;basket trap;seine;baited trap</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Biodiversity - visual &amp; video</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>Bird / shorebird counts</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Visual survey</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>bird;shorebird;scan</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>eDNA / genetic sampling</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Water eDNA</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>edna;12s;coi;18s;metabarcod;otu;sequenc</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>Filter -&gt; extract -&gt; sequence</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>eDNA / genetic sampling</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Settlement-plate DNA metabarcoding</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>settlement plate;metabarcod;otu</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Crop tissue &amp; performance</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Tissue elemental (CHN) analysis</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>Tissue analysis</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>tissue;chn;elemental;%n;%p;bioextract</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>%N/%P/%C; bioextraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
+        <is>
+          <t>Crop tissue &amp; performance</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>Stable isotopes (d13C / d15N)</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>Stable isotope analysis;Tissue analysis</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>isotope;delta-13-c;delta-15-n;irms</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Crop tissue &amp; performance</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>Bivalve condition index / growth</t>
+        </is>
+      </c>
+      <c r="D37" s="21" t="inlineStr">
+        <is>
+          <t>Bivalve performance / condition index</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>condition index;growth;performance</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>Crop tissue &amp; performance</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>Excretion (ammonium)</t>
+        </is>
+      </c>
+      <c r="D38" s="21" t="inlineStr">
+        <is>
+          <t>Tissue analysis</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>excret;ammonium excretion</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Crop tissue &amp; performance</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>Biosensor / valve-gape tag</t>
+        </is>
+      </c>
+      <c r="D39" s="21" t="inlineStr">
+        <is>
+          <t>Sensor / wearable tag</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="inlineStr">
+        <is>
+          <t>valve;gape;biosensor;wearable;tag</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Plankton &amp; phytoplankton</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Phytoplankton community (microscopy)</t>
+        </is>
+      </c>
+      <c r="D40" s="23" t="inlineStr">
+        <is>
+          <t>Phytoplankton sampling;Plankton sampling</t>
+        </is>
+      </c>
+      <c r="E40" s="23" t="inlineStr">
+        <is>
+          <t>phytoplankton;utermohl;microscop;lugol;biovolume</t>
+        </is>
+      </c>
+      <c r="F40" s="23" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Plankton &amp; phytoplankton</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>Zooplankton net haul</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Plankton sampling</t>
+        </is>
+      </c>
+      <c r="E41" s="23" t="inlineStr">
+        <is>
+          <t>zooplankton;ring net;net haul</t>
+        </is>
+      </c>
+      <c r="F41" s="23" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Plankton &amp; phytoplankton</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Flow cytometry</t>
+        </is>
+      </c>
+      <c r="D42" s="23" t="inlineStr">
+        <is>
+          <t>Plankton sampling</t>
+        </is>
+      </c>
+      <c r="E42" s="23" t="inlineStr">
+        <is>
+          <t>flow cytometr</t>
+        </is>
+      </c>
+      <c r="F42" s="23" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>Plankton &amp; phytoplankton</t>
+        </is>
+      </c>
+      <c r="C43" s="22" t="inlineStr">
+        <is>
+          <t>Size-fractionated pigments (HPLC)</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>Pigment HPLC;Plankton sampling</t>
+        </is>
+      </c>
+      <c r="E43" s="23" t="inlineStr">
+        <is>
+          <t>hplc;pigment;fucoxanthin;peridinin;size-fraction</t>
+        </is>
+      </c>
+      <c r="F43" s="23" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Plankton &amp; phytoplankton</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Clearance-rate / filtration assays</t>
+        </is>
+      </c>
+      <c r="D44" s="23" t="inlineStr">
+        <is>
+          <t>Clearance-rate assay</t>
+        </is>
+      </c>
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>clearance rate;filtration;flow-through chamber;seston</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Remote sensing</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>Satellite ocean colour (chl-a)</t>
+        </is>
+      </c>
+      <c r="D45" s="25" t="inlineStr">
+        <is>
+          <t>Remote sensing</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>satellite;ocean colour;modis;sentinel;landsat;chlorophyll</t>
+        </is>
+      </c>
+      <c r="F45" s="25" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Remote sensing</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>Drone / UAV imagery</t>
+        </is>
+      </c>
+      <c r="D46" s="25" t="inlineStr">
+        <is>
+          <t>Remote sensing</t>
+        </is>
+      </c>
+      <c r="E46" s="25" t="inlineStr">
+        <is>
+          <t>drone;uav;hyperspectral;multispectral</t>
+        </is>
+      </c>
+      <c r="F46" s="25" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>Remote sensing</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>Farm / bloom extent mapping</t>
+        </is>
+      </c>
+      <c r="D47" s="25" t="inlineStr">
+        <is>
+          <t>Remote sensing</t>
+        </is>
+      </c>
+      <c r="E47" s="25" t="inlineStr">
+        <is>
+          <t>farm-area;bloom;extent;classif;footprint</t>
+        </is>
+      </c>
+      <c r="F47" s="25" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B48" s="26" t="inlineStr">
+        <is>
+          <t>Currents, waves &amp; physical</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>ADCP (currents / waves)</t>
+        </is>
+      </c>
+      <c r="D48" s="27" t="inlineStr">
+        <is>
+          <t>Acoustic;Hydrodynamic measurement</t>
+        </is>
+      </c>
+      <c r="E48" s="27" t="inlineStr">
+        <is>
+          <t>adcp;acoustic doppler current;current profil</t>
+        </is>
+      </c>
+      <c r="F48" s="27" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>Currents, waves &amp; physical</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>ADV (turbulent flow / bed shear)</t>
+        </is>
+      </c>
+      <c r="D49" s="27" t="inlineStr">
+        <is>
+          <t>Acoustic;Hydrodynamic measurement</t>
+        </is>
+      </c>
+      <c r="E49" s="27" t="inlineStr">
+        <is>
+          <t>adv;acoustic doppler velocimeter;turbulent</t>
+        </is>
+      </c>
+      <c r="F49" s="27" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B50" s="26" t="inlineStr">
+        <is>
+          <t>Currents, waves &amp; physical</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>Wave-tide recorder</t>
+        </is>
+      </c>
+      <c r="D50" s="27" t="inlineStr">
+        <is>
+          <t>Hydrodynamic measurement</t>
+        </is>
+      </c>
+      <c r="E50" s="27" t="inlineStr">
+        <is>
+          <t>wave-tide;wave recorder;tide</t>
+        </is>
+      </c>
+      <c r="F50" s="27" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B51" s="26" t="inlineStr">
+        <is>
+          <t>Currents, waves &amp; physical</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>Passive acoustic (marine mammals)</t>
+        </is>
+      </c>
+      <c r="D51" s="27" t="inlineStr">
+        <is>
+          <t>Acoustic</t>
+        </is>
+      </c>
+      <c r="E51" s="27" t="inlineStr">
+        <is>
+          <t>click-detector;passive acoustic;marine mammal;detection-positive</t>
+        </is>
+      </c>
+      <c r="F51" s="27" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B52" s="26" t="inlineStr">
+        <is>
+          <t>Currents, waves &amp; physical</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Site exposure characterisation</t>
+        </is>
+      </c>
+      <c r="D52" s="27" t="inlineStr">
+        <is>
+          <t>Modelling;Hydrodynamic measurement</t>
+        </is>
+      </c>
+      <c r="E52" s="27" t="inlineStr">
+        <is>
+          <t>exposure;see;exposure velocity;wave-and-current</t>
+        </is>
+      </c>
+      <c r="F52" s="27" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B53" s="28" t="inlineStr">
+        <is>
+          <t>Modelling &amp; desk assessments</t>
+        </is>
+      </c>
+      <c r="C53" s="28" t="inlineStr">
+        <is>
+          <t>GIS siting / carrying capacity</t>
+        </is>
+      </c>
+      <c r="D53" s="29" t="inlineStr">
+        <is>
+          <t>Modelling</t>
+        </is>
+      </c>
+      <c r="E53" s="29" t="inlineStr">
+        <is>
+          <t>gis;suitability;carrying capacity;siting</t>
+        </is>
+      </c>
+      <c r="F53" s="29" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B54" s="28" t="inlineStr">
+        <is>
+          <t>Modelling &amp; desk assessments</t>
+        </is>
+      </c>
+      <c r="C54" s="28" t="inlineStr">
+        <is>
+          <t>Hydrodynamic + particle tracking</t>
+        </is>
+      </c>
+      <c r="D54" s="29" t="inlineStr">
+        <is>
+          <t>Modelling</t>
+        </is>
+      </c>
+      <c r="E54" s="29" t="inlineStr">
+        <is>
+          <t>particle-track;lagrangian;deposition footprint;hydrodynamic model</t>
+        </is>
+      </c>
+      <c r="F54" s="29" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>Modelling &amp; desk assessments</t>
+        </is>
+      </c>
+      <c r="C55" s="28" t="inlineStr">
+        <is>
+          <t>Coupled biogeochemical / DEB model</t>
+        </is>
+      </c>
+      <c r="D55" s="29" t="inlineStr">
+        <is>
+          <t>Modelling</t>
+        </is>
+      </c>
+      <c r="E55" s="29" t="inlineStr">
+        <is>
+          <t>biogeochem;dynamic-energy-budget;deb;coupled;ecosystem model</t>
+        </is>
+      </c>
+      <c r="F55" s="29" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>Modelling &amp; desk assessments</t>
+        </is>
+      </c>
+      <c r="C56" s="28" t="inlineStr">
+        <is>
+          <t>Wave-attenuation model</t>
+        </is>
+      </c>
+      <c r="D56" s="29" t="inlineStr">
+        <is>
+          <t>Modelling</t>
+        </is>
+      </c>
+      <c r="E56" s="29" t="inlineStr">
+        <is>
+          <t>wave attenuation;wave model;cross-shore</t>
+        </is>
+      </c>
+      <c r="F56" s="29" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="28" t="n">
+        <v>9</v>
+      </c>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>Modelling &amp; desk assessments</t>
+        </is>
+      </c>
+      <c r="C57" s="28" t="inlineStr">
+        <is>
+          <t>Nutrient mass-balance / budget</t>
+        </is>
+      </c>
+      <c r="D57" s="29" t="inlineStr">
+        <is>
+          <t>Modelling</t>
+        </is>
+      </c>
+      <c r="E57" s="29" t="inlineStr">
+        <is>
+          <t>mass-balance;budget;accounting;flux</t>
+        </is>
+      </c>
+      <c r="F57" s="29" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F57"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -3560,6 +5265,56 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Sheet 'Monitoring_Approaches': the 'What are you already monitoring?' screener. One row per</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sub_Method. Category_Order sets the order of the top-level yes/no buckets; rows sharing a</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Category are grouped under it; Sub_Methods show as checkboxes when that Category is answered yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Add/rename/reorder here and the screener updates on next app load (read by column header).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AG_Tags must match the 'Method Category' values in the literature database (mel_database.xlsx,</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>col AG); AK_Keywords are lowercase terms matched against 'Protocol Method Summary' (col AK).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>These drive the ranking BOOST only - the screener never filters protocols out.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
